--- a/dataset_t6_grouped/results2/G3/G3_T1829_W0042F0003T0006Z000C1N13_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G3/G3_T1829_W0042F0003T0006Z000C1N13_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>58.44140037439405</v>
+        <v>9.496727560839034</v>
       </c>
       <c r="D2" t="n">
-        <v>27.1451882300437</v>
+        <v>4.411093087382101</v>
       </c>
       <c r="E2" t="n">
-        <v>15.9165256089504</v>
+        <v>2.58643541145444</v>
       </c>
       <c r="F2" t="n">
-        <v>15.78533607563726</v>
+        <v>2.565117112291055</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>60.41565095321469</v>
+        <v>9.817543279897388</v>
       </c>
       <c r="D3" t="n">
-        <v>59.48287138793771</v>
+        <v>9.665966600539878</v>
       </c>
       <c r="E3" t="n">
-        <v>15.9165256089504</v>
+        <v>2.58643541145444</v>
       </c>
       <c r="F3" t="n">
-        <v>15.78533607563726</v>
+        <v>2.565117112291055</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>23.91093612146081</v>
+        <v>3.885527119737382</v>
       </c>
       <c r="D4" t="n">
-        <v>30.91524695395304</v>
+        <v>5.023727630017369</v>
       </c>
       <c r="E4" t="n">
-        <v>15.9165256089504</v>
+        <v>2.58643541145444</v>
       </c>
       <c r="F4" t="n">
-        <v>15.78533607563726</v>
+        <v>2.565117112291055</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>65.01852520581235</v>
+        <v>10.56551034594451</v>
       </c>
       <c r="D5" t="n">
-        <v>61.70000285150356</v>
+        <v>10.02625046336933</v>
       </c>
       <c r="E5" t="n">
-        <v>15.9165256089504</v>
+        <v>2.58643541145444</v>
       </c>
       <c r="F5" t="n">
-        <v>15.78533607563726</v>
+        <v>2.565117112291055</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>67.90952945465015</v>
+        <v>11.03529853638065</v>
       </c>
       <c r="D6" t="n">
-        <v>61.54412932093614</v>
+        <v>10.00092101465212</v>
       </c>
       <c r="E6" t="n">
-        <v>15.9165256089504</v>
+        <v>2.58643541145444</v>
       </c>
       <c r="F6" t="n">
-        <v>15.78533607563726</v>
+        <v>2.565117112291055</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>72.29901321163837</v>
+        <v>11.74858964689123</v>
       </c>
       <c r="D7" t="n">
-        <v>66.00293116628649</v>
+        <v>10.72547631452155</v>
       </c>
       <c r="E7" t="n">
-        <v>15.9165256089504</v>
+        <v>2.58643541145444</v>
       </c>
       <c r="F7" t="n">
-        <v>15.78533607563726</v>
+        <v>2.565117112291055</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
